--- a/config/rules/.history/PDS001MI.xlsx
+++ b/config/rules/.history/PDS001MI.xlsx
@@ -642,9 +642,14 @@
           <t>AOPL</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AOPL</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>IGNORE</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3142,7 +3147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4584,6 +4589,60 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:41:00</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AOPL</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Type: IGNORE-&gt;DIRECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-04-02 11:32:18</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AOPL</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Src: -&gt;AOPL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
